--- a/calculo_cd_experimental.xlsx
+++ b/calculo_cd_experimental.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tanque cuadrado" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jarra (tronco de cono)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incertidumbres" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +42,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="2">
@@ -69,7 +74,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -81,6 +86,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -58730,4 +58736,619 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Incertidumbre - Tanque cuadrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Parametros geometricos:</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Parametro</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Incertidumbre (±)</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Instrumento</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>a (m)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Regla</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>b (m)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Regla</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AT = a*b (m2)</t>
+        </is>
+      </c>
+      <c r="B7">
+        <f>B5*B6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>d_orificio (m)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.005642</v>
+      </c>
+      <c r="C8" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Calibre</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A0 = pi*d^2/4 (m2)</t>
+        </is>
+      </c>
+      <c r="B9">
+        <f>PI()*B8^2/4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>h0 (m)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Regla</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Incertidumbre instrumental (tipo B):</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Contribucion</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Valor (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>u(AT)/AT</t>
+        </is>
+      </c>
+      <c r="B14">
+        <f>SQRT((C5/B5)^2 + (C6/B6)^2)</f>
+        <v/>
+      </c>
+      <c r="C14">
+        <f>100*B14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>u(A0)/A0</t>
+        </is>
+      </c>
+      <c r="B15">
+        <f>2*C8/B8</f>
+        <v/>
+      </c>
+      <c r="C15">
+        <f>100*B15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>u(h0)/Cd (contrib)</t>
+        </is>
+      </c>
+      <c r="B16">
+        <f>C10/(2*SQRT(B10)*(SQRT(B10)-SQRT(B10/2)))</f>
+        <v/>
+      </c>
+      <c r="C16">
+        <f>100*B16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>u_sys/Cd (combinada)</t>
+        </is>
+      </c>
+      <c r="B17">
+        <f>SQRT(B14^2 + B15^2 + B16^2)</f>
+        <v/>
+      </c>
+      <c r="C17">
+        <f>100*B17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Resultados combinados:</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Fluido</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Cd</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>u_tipo_A (estad)</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>u_tipo_B (instr)</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>u_combinada</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Resultado final</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Agua</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.4164</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="D21">
+        <f>B21*B17</f>
+        <v/>
+      </c>
+      <c r="E21">
+        <f>SQRT(C21^2 + D21^2)</f>
+        <v/>
+      </c>
+      <c r="F21">
+        <f>B21 &amp; " ± " &amp; ROUND(E21, 4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Aceite</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.3983</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="D22">
+        <f>B22*B17</f>
+        <v/>
+      </c>
+      <c r="E22">
+        <f>SQRT(C22^2 + D22^2)</f>
+        <v/>
+      </c>
+      <c r="F22">
+        <f>B22 &amp; " ± " &amp; ROUND(E22, 4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Incertidumbre - Jarra troncoconica</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Parametros geometricos:</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Parametro</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Incertidumbre (±)</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Instrumento</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Rb (m)</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Calibre</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Rt (m)</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.0615</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Calibre</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>h0 (m)</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Regla</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>d_orificio (m)</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C32" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Calibre</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>A0 = pi*d^2/4 (m2)</t>
+        </is>
+      </c>
+      <c r="B33">
+        <f>PI()*B32^2/4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Incertidumbre instrumental (tipo B):</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>Nota: contribuciones obtenidas por derivacion numerica (diferencia central, paso 0.1%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Contribucion</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Valor relativo (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>u(Rb)/Cd</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.0044</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>u(Rt)/Cd</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.0122</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>u(h0)/Cd</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.0147</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>u(A0)/A0</t>
+        </is>
+      </c>
+      <c r="B41">
+        <f>2*C32/B32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>u_sys/Cd (combinada)</t>
+        </is>
+      </c>
+      <c r="B42">
+        <f>SQRT(B38^2 + B39^2 + B40^2 + B41^2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>Resultados combinados:</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Fluido</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>Cd</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>u_tipo_A (estad)</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>u_tipo_B (instr)</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>u_combinada</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>Resultado final</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Agua</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0.5899</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="D46">
+        <f>B46*B42</f>
+        <v/>
+      </c>
+      <c r="E46">
+        <f>SQRT(C46^2 + D46^2)</f>
+        <v/>
+      </c>
+      <c r="F46">
+        <f>B46 &amp; " ± " &amp; ROUND(E46, 4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Aceite</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0.4446</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="D47">
+        <f>B47*B42</f>
+        <v/>
+      </c>
+      <c r="E47">
+        <f>SQRT(C47^2 + D47^2)</f>
+        <v/>
+      </c>
+      <c r="F47">
+        <f>B47 &amp; " ± " &amp; ROUND(E47, 4)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A25:E25"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/calculo_cd_experimental.xlsx
+++ b/calculo_cd_experimental.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tanque cuadrado" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jarra (tronco de cono)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incertidumbres" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,6 +47,14 @@
     <font>
       <i val="1"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="2">
@@ -74,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -87,6 +96,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -59351,4 +59362,229 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Tabla 1. Incertidumbres instrumentales</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Magnitud</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Instrumento</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Incertidumbre</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Dimensiones del tanque (lados, radios)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Regla</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>±1 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Altura inicial h0</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Regla</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>±1 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Diametro del orificio do</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Calibre</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>±0.05 mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Tabla 2. Componentes de incertidumbre del coeficiente de descarga</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Configuracion</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>u_A (estad)</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>u_B (instr)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>u_total</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Resultado final</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Cuadrado - Agua</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0112</v>
+      </c>
+      <c r="D9">
+        <f>SQRT(B9^2+C9^2)</f>
+        <v/>
+      </c>
+      <c r="E9">
+        <f>0.4164 &amp; " ± " &amp; ROUND(D9,4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Cuadrado - Aceite</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0107</v>
+      </c>
+      <c r="D10">
+        <f>SQRT(B10^2+C10^2)</f>
+        <v/>
+      </c>
+      <c r="E10">
+        <f>0.3983 &amp; " ± " &amp; ROUND(D10,4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Jarra - Agua</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.0008</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="D11">
+        <f>SQRT(B11^2+C11^2)</f>
+        <v/>
+      </c>
+      <c r="E11">
+        <f>0.5899 &amp; " ± " &amp; ROUND(D11,4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Jarra - Aceite</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="D12">
+        <f>SQRT(B12^2+C12^2)</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>0.4446 &amp; " ± " &amp; ROUND(D12,4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Nota: u_B domina sobre u_A en todos los casos (~2.7% vs ~0.2% relativo).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A7:E7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>